--- a/Test/ユーザー登録 登録画面単体テストケース.xlsx
+++ b/Test/ユーザー登録 登録画面単体テストケース.xlsx
@@ -14,60 +14,317 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="303">
+  <si>
+    <t>名前（姓）=ひらがな・漢字・10文字以内</t>
+  </si>
   <si>
     <t>テストID</t>
   </si>
   <si>
+    <t>観点カテゴリ</t>
+  </si>
+  <si>
+    <t>実践課題：</t>
+  </si>
+  <si>
+    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
+  </si>
+  <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
+    <t>確認済</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>入力値検証</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>記載例</t>
+  </si>
+  <si>
+    <t>注意点</t>
+  </si>
+  <si>
+    <t>各テストケースを一意に識別するID</t>
+  </si>
+  <si>
+    <t>UT-001, UT-002</t>
+  </si>
+  <si>
+    <t>プロジェクト内で重複しないように採番</t>
+  </si>
+  <si>
     <t>機能名</t>
   </si>
   <si>
+    <t>テスト対象の機能やクラス名</t>
+  </si>
+  <si>
+    <t>ログイン認証、ユーザー登録</t>
+  </si>
+  <si>
+    <t>要件定義書・設計書と用語を統一</t>
+  </si>
+  <si>
     <t>テスト観点・目的</t>
   </si>
   <si>
+    <t>何を確認するテストか</t>
+  </si>
+  <si>
+    <t>入力値チェック、正常系動作確認</t>
+  </si>
+  <si>
+    <t>具体的な検証ポイントを明記</t>
+  </si>
+  <si>
     <t>前提条件</t>
   </si>
   <si>
+    <t>テスト実行前に整える条件</t>
+  </si>
+  <si>
+    <t>ログイン画面が表示されている状態</t>
+  </si>
+  <si>
+    <t>環境設定、データ状態なども記載</t>
+  </si>
+  <si>
     <t>テスト手順</t>
   </si>
   <si>
+    <t>具体的な実行ステップ</t>
+  </si>
+  <si>
+    <t>1. ユーザーID欄に入力
+2. ボタンをクリック</t>
+  </si>
+  <si>
+    <t>番号付きで誰でも実行できるよう詳細に</t>
+  </si>
+  <si>
+    <t>テストデータ</t>
+  </si>
+  <si>
+    <t>使用する入力値の詳細</t>
+  </si>
+  <si>
+    <t>ユーザーID=test001</t>
+  </si>
+  <si>
+    <t>正常値、境界値、異常値を網羅</t>
+  </si>
+  <si>
+    <t>期待結果</t>
+  </si>
+  <si>
+    <t>成功時に得られるべき出力</t>
+  </si>
+  <si>
+    <t>エラーメッセージ「〇〇」が表示</t>
+  </si>
+  <si>
+    <t>曖昧な表現を避け具体的に記載</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>テストの重要度</t>
+  </si>
+  <si>
+    <t>高・中・低</t>
+  </si>
+  <si>
+    <t>リスクや影響度に応じて設定</t>
+  </si>
+  <si>
+    <t>実施日</t>
+  </si>
+  <si>
+    <t>テスト実行日</t>
+  </si>
+  <si>
+    <t>2025/10/15</t>
+  </si>
+  <si>
+    <t>実行後に記入</t>
+  </si>
+  <si>
+    <t>実施者</t>
+  </si>
+  <si>
+    <t>テスト実行者名</t>
+  </si>
+  <si>
+    <t>山田太郎</t>
+  </si>
+  <si>
+    <t>実測結果</t>
+  </si>
+  <si>
+    <t>実際の出力結果</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示された</t>
+  </si>
+  <si>
+    <t>合否判定</t>
+  </si>
+  <si>
+    <t>期待結果との比較結果</t>
+  </si>
+  <si>
+    <t>○（合格）、×（不合格）</t>
+  </si>
+  <si>
+    <t>その他特記事項</t>
+  </si>
+  <si>
+    <t>不具合管理番号:BUG-123</t>
+  </si>
+  <si>
+    <t>必要に応じて追加情報を記載</t>
+  </si>
+  <si>
+    <t>【重要なポイント】</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>期待結果は具体的に記載し、曖昧な表現を避ける</t>
+  </si>
+  <si>
+    <t>テスト手順は番号を付けて、誰でも実行できるよう詳細に記載</t>
+  </si>
+  <si>
+    <t>正常値・境界値・異常値を網羅的にテストケース化</t>
+  </si>
+  <si>
+    <t>レビュー体制を構築し、複数人でチェック</t>
+  </si>
+  <si>
+    <t>要件定義書・設計書とのトレーサビリティを確保</t>
+  </si>
+  <si>
+    <t>名前（名）=ひらがな・漢字・10文字以内</t>
+  </si>
+  <si>
     <t>テストデータ（入力値）</t>
   </si>
   <si>
-    <t>期待結果</t>
-  </si>
-  <si>
-    <t>優先度</t>
-  </si>
-  <si>
-    <t>実施日</t>
-  </si>
-  <si>
-    <t>実施者</t>
-  </si>
-  <si>
-    <t>実測結果</t>
-  </si>
-  <si>
-    <t>合否判定</t>
-  </si>
-  <si>
-    <t>備考</t>
+    <t>参加時間：</t>
+  </si>
+  <si>
+    <t>正常値（代表値）のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>カナ（姓）=カタカナ・10文字以内</t>
+  </si>
+  <si>
+    <t>次回参加希望日時：</t>
+  </si>
+  <si>
+    <t>カナ（名）=カタカナ・10文字以内</t>
+  </si>
+  <si>
+    <t>□</t>
+  </si>
+  <si>
+    <t>課題：</t>
+  </si>
+  <si>
+    <t>メールアドレス=半角英数字・半角記号（ハイフン・アットマーク）・100文字以内</t>
+  </si>
+  <si>
+    <t>パスワード=半角英数字・10文字以内</t>
+  </si>
+  <si>
+    <t>郵便番号=半角数字・7文字以内</t>
+  </si>
+  <si>
+    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>空文字・Nullのテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字</t>
+  </si>
+  <si>
+    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字</t>
+  </si>
+  <si>
+    <t>機能動作</t>
+  </si>
+  <si>
+    <t>正常系の動作確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>UT-002</t>
   </si>
   <si>
     <t>UT-001</t>
   </si>
   <si>
+    <t>異常系のエラー処理ケースを作成したか</t>
+  </si>
+  <si>
     <t>ユーザー登録</t>
   </si>
   <si>
+    <t>例外処理の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>画面表示</t>
+  </si>
+  <si>
+    <t>期待する画面遷移のケースを作成したか</t>
+  </si>
+  <si>
+    <t>エラーメッセージ表示のケースを作成したか</t>
+  </si>
+  <si>
+    <t>必須項目のバリデーションケースを作成したか</t>
+  </si>
+  <si>
     <t>入力値チェック(分岐網羅・未入力)</t>
   </si>
   <si>
     <t>登録画面が表示されている状態</t>
   </si>
   <si>
+    <t>データ処理</t>
+  </si>
+  <si>
+    <t>正常系動作確認(命令網羅)</t>
+  </si>
+  <si>
+    <t>データベース登録・更新のケースを作成したか</t>
+  </si>
+  <si>
     <t>1. 全て入力していない項目欄を作る
+2. 確認するボタンをクリック</t>
+  </si>
+  <si>
+    <t>全ての項目を入力した際に確認画面に移行する</t>
+  </si>
+  <si>
+    <t>1. 登録画面の各項目に有効な値を入力
 2. 確認するボタンをクリック</t>
   </si>
   <si>
@@ -87,22 +344,103 @@
 2．登録画面に留まること</t>
   </si>
   <si>
+    <t>データベース削除のケースを作成したか</t>
+  </si>
+  <si>
+    <t>名前（姓）=佐々木
+名前（名）=美優
+カナ（姓）=ササキ
+カナ（名）=ミウ
+メールアドレス=miusasaki@gmail.com
+パスワード=miu0001
+郵便番号=1234567
+住所（市区町村）=学研都市試験村
+住所（番地）=99-99</t>
+  </si>
+  <si>
     <t>高</t>
   </si>
   <si>
+    <t>1. 確認画面に遷移すること
+2. 確認画面に入力した内容が表示されていること
+(パスワードに関しては入力した文字数分●表示されていること)</t>
+  </si>
+  <si>
+    <t>データ検索・取得のケースを作成したか</t>
+  </si>
+  <si>
+    <t>権限・認証</t>
+  </si>
+  <si>
+    <t>UT-003</t>
+  </si>
+  <si>
+    <t>権限チェックのケースを作成したか</t>
+  </si>
+  <si>
+    <t>入力値チェック(分岐網羅・指定文字種以外の入力)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 各項目、指定されていない文字種を入力する
+2.確認するボタンをクリック
+</t>
+  </si>
+  <si>
+    <t>ログイン状態の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>名前（姓）＝Ituki
+名前（名）＝Shu
+カナ（姓）=斎宮
+カナ（名）=宗
+メールアドレス=ヴァルパリ＊スクエア
+パスワード=ミカ・マドモアゼル
+郵便番号=Ansan
+住所（市区町村）=＊＊＊＊＊＊square
+住所（番地）=VMS</t>
+  </si>
+  <si>
+    <t>1. 入力した項目にエラーメッセージが表示される
+2. 登録画面に留まること</t>
+  </si>
+  <si>
     <t>山本穂乃花</t>
   </si>
   <si>
-    <t>一番上の「名前（姓）」の欄に「このフィールドを入力してください。」というエラーメッセージが表示され登録画面に留まるが、他項目にメッセージが表示されない</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>一項目エラー発生していると他項目にエラーメッセージが表示されないため、複数のエラーがあった際にどこにエラーがあったか気づきにくい。</t>
-  </si>
-  <si>
-    <t>UT-002</t>
+    <t>一番上の「名前（姓）」の欄に「このフィールドを入力してください。」というエラーメッセージが表示され登録画面に留まった。</t>
+  </si>
+  <si>
+    <t>合</t>
+  </si>
+  <si>
+    <t>メモ</t>
+  </si>
+  <si>
+    <t>テストパターン</t>
+  </si>
+  <si>
+    <t>命令網羅</t>
+  </si>
+  <si>
+    <t>全ての処理を一度は通すこと(上手く処理できてるか)</t>
+  </si>
+  <si>
+    <t>分岐網羅</t>
+  </si>
+  <si>
+    <t>全ての分岐を一度通すこと</t>
+  </si>
+  <si>
+    <t>指示書では「エラー部分には赤いエラーメッセージを表示」とあるが、「regist.php」において「requiredコード」で入力必須の属性を付与しているためデフォルトのエラーメッセージ(吹き出しが出て、「！このフィールドを入力してください。」)が表示される。</t>
+  </si>
+  <si>
+    <t>条件網羅</t>
+  </si>
+  <si>
+    <t>個々の条件を最低1回は満たすようにテストすること</t>
+  </si>
+  <si>
+    <t>例は可能な入力種の説明を書きこんで</t>
   </si>
   <si>
     <t>入力値チェック(条件網羅・未入力)</t>
@@ -141,12 +479,6 @@
     <t>「名前（姓）」の欄に「このフィールドを入力してください」のエラーメッセージが表示され、登録画面に留まる</t>
   </si>
   <si>
-    <t>合</t>
-  </si>
-  <si>
-    <t>UT-003</t>
-  </si>
-  <si>
     <t>1. 名前（名）だけを入力していない項目欄を作る
 2. 確認するボタンをクリック</t>
   </si>
@@ -507,7 +839,7 @@
 それ以外の欄は空白</t>
   </si>
   <si>
-    <t>一番上の「名前（名）」の欄に「このフィールドを入力してください。」というエラーメッセージが表示され登録画面に留まるが、他項目にメッセージが表示されない</t>
+    <t>一番上の「名前（名）」の欄に「このフィールドを入力してください。」というエラーメッセージが表示され登録画面に留まった。</t>
   </si>
   <si>
     <t>UT-012</t>
@@ -599,9 +931,6 @@
   </si>
   <si>
     <t>UT-020</t>
-  </si>
-  <si>
-    <t>入力値チェック(分岐網羅・指定文字種以外の入力)</t>
   </si>
   <si>
     <t xml:space="preserve">1. 名前（姓）にカタカナを入力する
@@ -651,10 +980,6 @@
     </r>
   </si>
   <si>
-    <t>1. 入力した項目にエラーメッセージが表示される
-2. 登録画面に留まること</t>
-  </si>
-  <si>
     <t>「名前（姓）」の欄に「指定されている形式で入力してください」というエラーメッセージが表示され、登録画面に留まる。</t>
   </si>
   <si>
@@ -1239,10 +1564,23 @@
     </r>
   </si>
   <si>
-    <t>情報確認画面に移行してしまった</t>
-  </si>
-  <si>
-    <t>メールアドレスのパターンで指定した文字種を確認する必要あり</t>
+    <t>2026/02/04
+↓
+2026/09/03</t>
+  </si>
+  <si>
+    <t>情報確認画面に移行してしまった
+↓
+エラーメッセージが出て登録画面に留まった。</t>
+  </si>
+  <si>
+    <t>否
+↓
+合</t>
+  </si>
+  <si>
+    <t>「input type」を「text」から「email」に変更
+（2026/09/03更新）</t>
   </si>
   <si>
     <t>UT-031</t>
@@ -1829,7 +2167,7 @@
     <t>テキストボックス上に10文字以上入力すると10文字目以降は消えてしまう為そもそも入力することが出来ない。</t>
   </si>
   <si>
-    <t>（文字数制限を守れるという意味では）合だが、（エラー表示という意味では）否</t>
+    <t>「maxlength」で字数制限をしているため、エラーメッセージが表示されず規定文字数以上の文字が入力できないようになっている。</t>
   </si>
   <si>
     <t>UT-041</t>
@@ -2291,16 +2629,6 @@
     <t>UT-050</t>
   </si>
   <si>
-    <t>正常系動作確認(命令網羅)</t>
-  </si>
-  <si>
-    <t>全ての項目を入力した際に確認画面に移行する</t>
-  </si>
-  <si>
-    <t>1. 登録画面の各項目に有効な値を入力
-2. 確認するボタンをクリック</t>
-  </si>
-  <si>
     <t>名前（姓）=ひらがな・漢字・10文字以内
 名前（名）=ひらがな・漢字・10文字以内
 カナ（姓）=カタカナ・10文字以内
@@ -2312,325 +2640,29 @@
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字</t>
   </si>
   <si>
-    <t>1. 確認画面に遷移すること
-2. 確認画面に入力した内容が表示されていること
-(パスワードに関しては入力した文字数分●表示されていること)</t>
-  </si>
-  <si>
     <t>確認画面に遷移し入力内容が表示された</t>
   </si>
   <si>
-    <t>名前（姓）=ひらがな・漢字・10文字以内</t>
-  </si>
-  <si>
-    <t>実践課題：</t>
-  </si>
-  <si>
-    <t>名前（名）=ひらがな・漢字・10文字以内</t>
-  </si>
-  <si>
-    <t>参加時間：</t>
-  </si>
-  <si>
-    <t>カナ（姓）=カタカナ・10文字以内</t>
-  </si>
-  <si>
-    <t>次回参加希望日時：</t>
-  </si>
-  <si>
-    <t>カナ（名）=カタカナ・10文字以内</t>
-  </si>
-  <si>
-    <t>課題：</t>
-  </si>
-  <si>
-    <t>メールアドレス=半角英数字・半角記号（ハイフン・アットマーク）・100文字以内</t>
-  </si>
-  <si>
-    <t>パスワード=半角英数字・10文字以内</t>
-  </si>
-  <si>
-    <t>郵便番号=半角数字・7文字以内</t>
-  </si>
-  <si>
-    <t>住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字</t>
-  </si>
-  <si>
-    <t>住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字</t>
-  </si>
-  <si>
-    <t>名前（姓）=佐々木
-名前（名）=美優
-カナ（姓）=ササキ
-カナ（名）=ミウ
-メールアドレス=miusasaki@gmail.com
-パスワード=miu0001
-郵便番号=1234567
-住所（市区町村）=学研都市試験村
-住所（番地）=99-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 各項目、指定されていない文字種を入力する
-2.確認するボタンをクリック
+    <t>UT-051</t>
+  </si>
+  <si>
+    <t>ホーム画面が表示されている状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ホーム画面からアカウント登録を選択する
 </t>
   </si>
   <si>
-    <t>名前（姓）＝Ituki
-名前（名）＝Shu
-カナ（姓）=斎宮
-カナ（名）=宗
-メールアドレス=ヴァルパリ＊スクエア
-パスワード=ミカ・マドモアゼル
-郵便番号=Ansan
-住所（市区町村）=＊＊＊＊＊＊square
-住所（番地）=VMS</t>
-  </si>
-  <si>
-    <t>メモ</t>
-  </si>
-  <si>
-    <t>テストパターン</t>
-  </si>
-  <si>
-    <t>命令網羅</t>
-  </si>
-  <si>
-    <t>全ての処理を一度は通すこと(上手く処理できてるか)</t>
-  </si>
-  <si>
-    <t>分岐網羅</t>
-  </si>
-  <si>
-    <t>全ての分岐を一度通すこと</t>
-  </si>
-  <si>
-    <t>条件網羅</t>
-  </si>
-  <si>
-    <t>個々の条件を最低1回は満たすようにテストすること</t>
-  </si>
-  <si>
-    <t>例は可能な入力種の説明を書きこんで</t>
-  </si>
-  <si>
-    <t>観点カテゴリ</t>
-  </si>
-  <si>
-    <t>チェック項目</t>
-  </si>
-  <si>
-    <t>確認済</t>
-  </si>
-  <si>
-    <t>入力値検証</t>
-  </si>
-  <si>
-    <t>正常値（代表値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>空文字・Nullのテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>不正な形式・特殊文字のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>機能動作</t>
-  </si>
-  <si>
-    <t>正常系の動作確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>異常系のエラー処理ケースを作成したか</t>
-  </si>
-  <si>
-    <t>例外処理の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>画面表示</t>
-  </si>
-  <si>
-    <t>期待する画面遷移のケースを作成したか</t>
-  </si>
-  <si>
-    <t>エラーメッセージ表示のケースを作成したか</t>
-  </si>
-  <si>
-    <t>必須項目のバリデーションケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ処理</t>
-  </si>
-  <si>
-    <t>データベース登録・更新のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データベース削除のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ検索・取得のケースを作成したか</t>
-  </si>
-  <si>
-    <t>権限・認証</t>
-  </si>
-  <si>
-    <t>権限チェックのケースを作成したか</t>
-  </si>
-  <si>
-    <t>ログイン状態の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>記載例</t>
-  </si>
-  <si>
-    <t>注意点</t>
-  </si>
-  <si>
-    <t>各テストケースを一意に識別するID</t>
-  </si>
-  <si>
-    <t>UT-001, UT-002</t>
-  </si>
-  <si>
-    <t>プロジェクト内で重複しないように採番</t>
-  </si>
-  <si>
-    <t>テスト対象の機能やクラス名</t>
-  </si>
-  <si>
-    <t>ログイン認証、ユーザー登録</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書と用語を統一</t>
-  </si>
-  <si>
-    <t>何を確認するテストか</t>
-  </si>
-  <si>
-    <t>入力値チェック、正常系動作確認</t>
-  </si>
-  <si>
-    <t>具体的な検証ポイントを明記</t>
-  </si>
-  <si>
-    <t>テスト実行前に整える条件</t>
-  </si>
-  <si>
-    <t>ログイン画面が表示されている状態</t>
-  </si>
-  <si>
-    <t>環境設定、データ状態なども記載</t>
-  </si>
-  <si>
-    <t>具体的な実行ステップ</t>
-  </si>
-  <si>
-    <t>1. ユーザーID欄に入力
-2. ボタンをクリック</t>
-  </si>
-  <si>
-    <t>番号付きで誰でも実行できるよう詳細に</t>
-  </si>
-  <si>
-    <t>テストデータ</t>
-  </si>
-  <si>
-    <t>使用する入力値の詳細</t>
-  </si>
-  <si>
-    <t>ユーザーID=test001</t>
-  </si>
-  <si>
-    <t>正常値、境界値、異常値を網羅</t>
-  </si>
-  <si>
-    <t>成功時に得られるべき出力</t>
-  </si>
-  <si>
-    <t>エラーメッセージ「〇〇」が表示</t>
-  </si>
-  <si>
-    <t>曖昧な表現を避け具体的に記載</t>
-  </si>
-  <si>
-    <t>テストの重要度</t>
-  </si>
-  <si>
-    <t>高・中・低</t>
-  </si>
-  <si>
-    <t>リスクや影響度に応じて設定</t>
-  </si>
-  <si>
-    <t>テスト実行日</t>
-  </si>
-  <si>
-    <t>2025/10/15</t>
-  </si>
-  <si>
-    <t>実行後に記入</t>
-  </si>
-  <si>
-    <t>テスト実行者名</t>
-  </si>
-  <si>
-    <t>山田太郎</t>
-  </si>
-  <si>
-    <t>実際の出力結果</t>
-  </si>
-  <si>
-    <t>エラーメッセージが表示された</t>
-  </si>
-  <si>
-    <t>期待結果との比較結果</t>
-  </si>
-  <si>
-    <t>○（合格）、×（不合格）</t>
-  </si>
-  <si>
-    <t>その他特記事項</t>
-  </si>
-  <si>
-    <t>不具合管理番号:BUG-123</t>
-  </si>
-  <si>
-    <t>必要に応じて追加情報を記載</t>
-  </si>
-  <si>
-    <t>【重要なポイント】</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>期待結果は具体的に記載し、曖昧な表現を避ける</t>
-  </si>
-  <si>
-    <t>テスト手順は番号を付けて、誰でも実行できるよう詳細に記載</t>
-  </si>
-  <si>
-    <t>正常値・境界値・異常値を網羅的にテストケース化</t>
-  </si>
-  <si>
-    <t>レビュー体制を構築し、複数人でチェック</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書とのトレーサビリティを確保</t>
+    <t>1.「D.I.BLOG」のトップ画面を表示
+2.ヘッドのメニューにある「ユーザ登録」をクリック</t>
+  </si>
+  <si>
+    <t>1．ユーザ登録画面に遷移すること
+2．アドレス欄に「http://localhost/Registration_sample/regist.php」と表示されていること</t>
+  </si>
+  <si>
+    <t>ユーザ登録画面に遷移し、アドレス欄に「http://localhost/Registration_sample/regist.php
+(見える範囲はlocalhost/Registration_sample/regist.php)」と表示された。</t>
   </si>
 </sst>
 </file>
@@ -2648,31 +2680,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF242424"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -2690,6 +2707,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FFC00000"/>
@@ -2701,6 +2723,16 @@
       <color rgb="FF70AD47"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF242424"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2767,41 +2799,41 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3047,1980 +3079,2022 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="A2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>24</v>
+      <c r="J2" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="A3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="2"/>
+      <c r="J3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="A4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="2"/>
+      <c r="J4" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="A5" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="2"/>
+      <c r="J5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="A6" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="2"/>
+      <c r="J6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="A7" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="2"/>
+      <c r="J7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="A8" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="2"/>
+      <c r="J8" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="4">
+      <c r="A9" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="2"/>
+      <c r="J9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="A10" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="2"/>
+      <c r="J10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="M10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="A11" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="2"/>
+      <c r="J11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="A12" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J12" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" s="12"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="4">
+      <c r="A13" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J13" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M13" s="12"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="A14" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J14" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M14" s="12"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="4">
+      <c r="A15" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J15" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M15" s="12"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="4">
+      <c r="A16" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J16" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M16" s="12"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="A17" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J17" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="12"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="A18" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J18" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="4">
+      <c r="A19" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J19" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="12"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="A20" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="4">
+      <c r="C20" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J20" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="12"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="4">
+      <c r="A21" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="13">
         <v>46044.0</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="J21" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="13">
+        <v>46044.0</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I26" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="13">
+        <v>45326.0</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M30" s="7"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M35" s="7"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I37" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I38" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M39" s="7"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I40" s="13">
+        <v>46057.0</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I41" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I42" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I43" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I46" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M46" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I47" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="L47" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I48" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M48" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I49" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="L49" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="4">
-        <v>46044.0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M22" s="2"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="D50" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="E50" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M24" s="2"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="F50" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" s="2"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" s="4">
-        <v>45326.0</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="2"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="I50" s="13">
+        <v>46065.0</v>
+      </c>
+      <c r="J50" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="3" t="s">
+      <c r="K50" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="L50" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M28" s="2"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="M50" s="7"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I51" s="13">
+        <v>46268.0</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="L51" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M37" s="2"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="4">
-        <v>46057.0</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" s="2"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M42" s="2"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M43" s="2"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M45" s="2"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M46" s="2"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M48" s="2"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M49" s="2"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="4">
-        <v>46065.0</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M50" s="2"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1"/>
+      <c r="M51" s="7"/>
+    </row>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
@@ -5077,34 +5151,34 @@
     <row r="105" ht="15.75" customHeight="1"/>
     <row r="106" ht="15.75" customHeight="1"/>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="2"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7"/>
+      <c r="M107" s="7"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="2"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+      <c r="M108" s="7"/>
     </row>
     <row r="109" ht="15.75" customHeight="1"/>
     <row r="110" ht="15.75" customHeight="1"/>
@@ -6014,161 +6088,161 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>199</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>201</v>
+      <c r="A2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>203</v>
+      <c r="A3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>205</v>
+      <c r="A4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>206</v>
+      <c r="A5" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>207</v>
+      <c r="A6" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>208</v>
+      <c r="A7" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>209</v>
+      <c r="A8" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>210</v>
+      <c r="A9" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="A12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="A13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>214</v>
+      <c r="A15" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>215</v>
+      <c r="A16" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>217</v>
+      <c r="A17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>219</v>
+      <c r="A18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>221</v>
+      <c r="A19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
-        <v>222</v>
+      <c r="A21" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -6191,198 +6265,198 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="A6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="A7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="A8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="A9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="A10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="A11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="A12" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="A13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="A14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="A15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="A16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="7"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -7387,252 +7461,252 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>251</v>
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>254</v>
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>257</v>
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>260</v>
+      <c r="A6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>263</v>
+      <c r="A7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>266</v>
+      <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>270</v>
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>273</v>
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>288</v>
+      <c r="B16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>289</v>
+      <c r="A18" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>291</v>
+      <c r="A19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>292</v>
+      <c r="A20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>293</v>
+      <c r="A21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>294</v>
+      <c r="A22" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>295</v>
+      <c r="A23" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
